--- a/Data/EXCEL/Transfer/salemon/20240711/8467-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/8467-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B6AC610-8F3E-4165-9624-61A28A8D8900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22036CC9-4094-4B9E-949F-550E1F95C44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{647DF3AE-772C-4257-AC1A-26D6A16CECDE}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{8B8D5C58-DC78-403B-99C7-62F5D74D5505}"/>
   </bookViews>
   <sheets>
     <sheet name="8467-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,18 +1261,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8698181A-AEDA-4B9C-A4FE-6185465C55AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D28BD7-4A31-49F9-B3B9-1781BF0751BF}">
   <dimension ref="A1:Q218"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1299,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1381,7 +1381,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1420,7 +1420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>45413</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>40.4</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>45352</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>45292</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>45231</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>-2.13</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>45170</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>-4.58</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>-7.68</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>45108</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>-5.81</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>45047</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>-10.3</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>-12.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>44986</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>-9.0500000000000007</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>44927</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>-45.4</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>44866</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>44805</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>44743</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>66.3</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>44682</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>44621</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>44562</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>222.6</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>44501</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>44440</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>44378</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>44317</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>44256</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>42.8</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>44197</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>-35.1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>-28</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>44136</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>-28.6</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>-27.5</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>44075</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>-25.9</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>-24</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>44013</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>-21.9</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>-26.6</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>43952</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>-15.4</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>-31.9</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>43891</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>-24</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>-20.2</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>43831</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>-2.75</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>-3.23</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>43770</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>-5.53</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>-5.48</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>43709</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>-7.08</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>43647</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>-9.02</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>-2.17</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>43586</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>-10.6</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>-3.01</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>43525</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>-15.8</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>-30.7</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>43466</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>-39.299999999999997</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>-5.03</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>43405</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>-1.49</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>43344</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>43282</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>43221</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>43160</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>43101</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>93.7</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5607,7 +5607,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>43040</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>42979</v>
       </c>
@@ -5766,7 +5766,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>42917</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>-1.35</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>-11.3</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>42856</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>-23.1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>42795</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>-12.5</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6137,7 +6137,7 @@
         <v>-14.3</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>42736</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>-22.4</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>-23.4</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>42675</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>-22.6</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>-18.3</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
         <v>42614</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>-20.9</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>-26.8</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>42552</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>-29.7</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>-26.7</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>42491</v>
       </c>
@@ -6614,7 +6614,7 @@
         <v>-19.3</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6667,7 +6667,7 @@
         <v>-21.1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>42430</v>
       </c>
@@ -6720,7 +6720,7 @@
         <v>-21.8</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>-4.4400000000000004</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
         <v>42370</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>-22.9</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6879,7 +6879,7 @@
         <v>-14.6</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>42309</v>
       </c>
@@ -6932,552 +6932,552 @@
         <v>-13.3</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="9">
         <v>45413</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="9">
         <v>45352</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
         <v>45292</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="9">
         <v>45231</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="9">
         <v>45170</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="9">
         <v>45108</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="9">
         <v>45047</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="9">
         <v>44986</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="9">
         <v>44927</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="9">
         <v>44866</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>44805</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="9">
         <v>44743</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>44682</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>44621</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="9">
         <v>44562</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>44501</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="9">
         <v>44440</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="9">
         <v>44378</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="9">
         <v>44317</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="9">
         <v>44256</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="9">
         <v>44136</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="9">
         <v>44075</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="9">
         <v>44013</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="9">
         <v>43952</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="9">
         <v>43891</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="9">
         <v>43831</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>43770</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="9">
         <v>43709</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="9">
         <v>43647</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="9">
         <v>43586</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="9">
         <v>43525</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="9">
         <v>43466</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="9">
         <v>43405</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="9">
         <v>43344</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="9">
         <v>43282</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="9">
         <v>43221</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="9">
         <v>43160</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="9">
         <v>43101</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="9">
         <v>43040</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="9">
         <v>42979</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="9">
         <v>42917</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="9">
         <v>42856</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="9">
         <v>42795</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="9">
         <v>42736</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="9">
         <v>42675</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="9">
         <v>42614</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="9">
         <v>42552</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="9">
         <v>42491</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="9">
         <v>42430</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="9">
         <v>42370</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="9">
         <v>42309</v>
       </c>
